--- a/Pruebas calificadas/COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)-901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)-901_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3257,11 +3217,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -3269,7 +3225,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3510,11 +3466,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -3522,7 +3474,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3763,11 +3715,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -3775,7 +3723,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4016,11 +3964,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -4028,7 +3972,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4269,11 +4213,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -4281,7 +4221,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4522,11 +4462,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -4534,7 +4470,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4775,11 +4711,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -4787,7 +4719,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5028,11 +4960,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -5040,7 +4968,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5281,11 +5209,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -5293,7 +5217,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5534,11 +5458,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -5546,7 +5466,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5787,11 +5707,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -5799,7 +5715,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6040,11 +5956,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -6052,7 +5964,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6293,11 +6205,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -6305,7 +6213,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6542,11 +6450,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -6554,7 +6458,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6791,11 +6695,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -6803,7 +6703,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7044,11 +6944,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -7056,7 +6952,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7297,11 +7193,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -7309,7 +7201,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7550,11 +7442,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -7562,7 +7450,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7803,11 +7691,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -7815,7 +7699,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8056,11 +7940,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -8068,7 +7948,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8309,11 +8189,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -8321,7 +8197,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8562,11 +8438,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -8574,7 +8446,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8815,11 +8687,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -8827,7 +8695,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9068,11 +8936,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -9080,7 +8944,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9317,11 +9181,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -9329,7 +9189,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9570,11 +9430,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -9582,7 +9438,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9823,11 +9679,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -9835,7 +9687,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10076,11 +9928,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -10088,7 +9936,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10329,11 +10177,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -10341,7 +10185,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10582,11 +10426,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -10594,7 +10434,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10835,11 +10675,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -10847,7 +10683,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11088,11 +10924,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -11100,7 +10932,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11341,11 +11173,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -11353,7 +11181,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11594,11 +11422,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -11606,7 +11430,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11847,11 +11671,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -11859,7 +11679,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12096,11 +11916,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -12108,7 +11924,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12349,11 +12165,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -12361,7 +12173,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12602,11 +12414,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -12614,7 +12422,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12855,11 +12663,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -12867,7 +12671,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13108,11 +12912,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -13120,7 +12920,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13361,11 +13161,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -13373,7 +13169,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13614,11 +13410,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -13626,7 +13418,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13867,11 +13659,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -13879,7 +13667,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14120,11 +13908,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -14132,7 +13916,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14373,11 +14157,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -14385,7 +14165,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14626,11 +14406,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -14638,7 +14414,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14879,11 +14655,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -14891,7 +14663,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15132,11 +14904,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -15144,7 +14912,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15385,11 +15153,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -15397,7 +15161,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15638,11 +15402,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -15650,7 +15410,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15891,11 +15651,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -15903,7 +15659,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16144,11 +15900,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -16156,7 +15908,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16397,11 +16149,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -16409,7 +16157,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16650,11 +16398,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -16662,7 +16406,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16903,11 +16647,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -16915,7 +16655,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17152,11 +16892,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -17164,7 +16900,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17405,11 +17141,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -17417,7 +17149,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17658,11 +17390,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -17670,7 +17398,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17911,11 +17639,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -17923,7 +17647,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18164,11 +17888,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -18176,7 +17896,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18417,11 +18137,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -18429,7 +18145,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18670,11 +18386,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -18682,7 +18394,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18923,11 +18635,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -18935,7 +18643,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19176,11 +18884,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -19188,7 +18892,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19429,11 +19133,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -19441,7 +19141,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19682,11 +19382,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -19694,7 +19390,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19935,11 +19631,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -19947,7 +19639,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20188,11 +19880,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -20200,7 +19888,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -20441,11 +20129,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -20453,7 +20137,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -20694,11 +20378,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -20706,7 +20386,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -20947,11 +20627,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -20959,7 +20635,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -21200,11 +20876,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -21212,7 +20884,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -21453,11 +21125,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -21465,7 +21133,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -21706,11 +21374,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -21718,7 +21382,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -21959,11 +21623,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -21971,7 +21631,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -22212,11 +21872,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -22224,7 +21880,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -22465,11 +22121,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -22477,7 +22129,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -22718,11 +22370,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
           <t>111001032395</t>
@@ -22730,7 +22378,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO REPUBLICA EE.UU. DE AMERICA (IED)</t>
+          <t>REPUBLICA EE.UU. DE AMERICA</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
